--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/19.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/19.xlsx
@@ -426,13 +426,13 @@
         <v>-6.913127630481565</v>
       </c>
       <c r="E2">
-        <v>-21.95705097263459</v>
+        <v>-33.99348581895197</v>
       </c>
       <c r="F2">
-        <v>-3.084069973588263</v>
+        <v>-5.022033855702901</v>
       </c>
       <c r="G2">
-        <v>-13.90920692046037</v>
+        <v>-20.39303947039902</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.21134811612412</v>
       </c>
       <c r="E3">
-        <v>-22.30941606364543</v>
+        <v>-34.06048006342145</v>
       </c>
       <c r="F3">
-        <v>-3.141256317240527</v>
+        <v>-4.949923644921801</v>
       </c>
       <c r="G3">
-        <v>-13.86527432588147</v>
+        <v>-20.20119832221656</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.442942240274159</v>
       </c>
       <c r="E4">
-        <v>-21.98625510151005</v>
+        <v>-34.30939442996407</v>
       </c>
       <c r="F4">
-        <v>-3.051930146727045</v>
+        <v>-5.061623190617495</v>
       </c>
       <c r="G4">
-        <v>-13.25419396696956</v>
+        <v>-20.22867253964698</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.562476099280389</v>
       </c>
       <c r="E5">
-        <v>-22.80594512469045</v>
+        <v>-34.96784360762735</v>
       </c>
       <c r="F5">
-        <v>-2.938742024808521</v>
+        <v>-4.947807994575051</v>
       </c>
       <c r="G5">
-        <v>-13.43709167637767</v>
+        <v>-19.98275528535329</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.568780365736462</v>
       </c>
       <c r="E6">
-        <v>-23.39125491865585</v>
+        <v>-34.86919759408126</v>
       </c>
       <c r="F6">
-        <v>-2.980934918470113</v>
+        <v>-5.009569411392977</v>
       </c>
       <c r="G6">
-        <v>-13.0157221295937</v>
+        <v>-20.07097304761102</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.443883491220122</v>
       </c>
       <c r="E7">
-        <v>-23.83672090679038</v>
+        <v>-35.50094688899532</v>
       </c>
       <c r="F7">
-        <v>-2.974520041302834</v>
+        <v>-5.068233562491835</v>
       </c>
       <c r="G7">
-        <v>-12.93520304098754</v>
+        <v>-19.78174392602705</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.189534419468742</v>
       </c>
       <c r="E8">
-        <v>-23.53905072484419</v>
+        <v>-35.34033550136528</v>
       </c>
       <c r="F8">
-        <v>-2.866271474207203</v>
+        <v>-4.792977843317796</v>
       </c>
       <c r="G8">
-        <v>-12.67562647579883</v>
+        <v>-19.45851053593647</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.80100940554224</v>
       </c>
       <c r="E9">
-        <v>-24.94193574462841</v>
+        <v>-36.2687904132619</v>
       </c>
       <c r="F9">
-        <v>-2.822891530057399</v>
+        <v>-4.840483057133541</v>
       </c>
       <c r="G9">
-        <v>-12.42449511228079</v>
+        <v>-19.42113778734363</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.277121619256708</v>
       </c>
       <c r="E10">
-        <v>-24.78276894020681</v>
+        <v>-36.46883801678774</v>
       </c>
       <c r="F10">
-        <v>-2.693574266438965</v>
+        <v>-4.779033934826471</v>
       </c>
       <c r="G10">
-        <v>-12.20112267310955</v>
+        <v>-19.3589723632072</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.625122915749781</v>
       </c>
       <c r="E11">
-        <v>-25.57705422420417</v>
+        <v>-36.94397003814652</v>
       </c>
       <c r="F11">
-        <v>-2.604547136557894</v>
+        <v>-4.861210466286391</v>
       </c>
       <c r="G11">
-        <v>-11.80343676911352</v>
+        <v>-19.09403768006317</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.847299973177472</v>
       </c>
       <c r="E12">
-        <v>-25.85265715231099</v>
+        <v>-37.16928652663517</v>
       </c>
       <c r="F12">
-        <v>-2.68323127104761</v>
+        <v>-4.777861794951511</v>
       </c>
       <c r="G12">
-        <v>-11.627080697691</v>
+        <v>-18.99069403523652</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.948623440252663</v>
       </c>
       <c r="E13">
-        <v>-26.60796133205033</v>
+        <v>-37.58150445860539</v>
       </c>
       <c r="F13">
-        <v>-2.716091777549264</v>
+        <v>-4.763961789932535</v>
       </c>
       <c r="G13">
-        <v>-11.57017241987093</v>
+        <v>-18.5052455689944</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.943535007856337</v>
       </c>
       <c r="E14">
-        <v>-27.54702193007292</v>
+        <v>-38.07115476763276</v>
       </c>
       <c r="F14">
-        <v>-2.399363844354067</v>
+        <v>-4.737227888741987</v>
       </c>
       <c r="G14">
-        <v>-10.90702049017183</v>
+        <v>-18.33314189331708</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.841978307834119</v>
       </c>
       <c r="E15">
-        <v>-28.41398016494538</v>
+        <v>-38.6264996490894</v>
       </c>
       <c r="F15">
-        <v>-2.262207740002942</v>
+        <v>-4.492553837344499</v>
       </c>
       <c r="G15">
-        <v>-10.80386720171368</v>
+        <v>-17.92881337969651</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6677960559698607</v>
       </c>
       <c r="E16">
-        <v>-28.22640171459965</v>
+        <v>-38.853557335834</v>
       </c>
       <c r="F16">
-        <v>-2.109939729122545</v>
+        <v>-4.422840921827101</v>
       </c>
       <c r="G16">
-        <v>-10.65317447931159</v>
+        <v>-17.95983153612671</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.5493420035335767</v>
       </c>
       <c r="E17">
-        <v>-29.42091353139492</v>
+        <v>-39.62126727011735</v>
       </c>
       <c r="F17">
-        <v>-1.857474882301729</v>
+        <v>-4.460876239494043</v>
       </c>
       <c r="G17">
-        <v>-10.05470067781322</v>
+        <v>-17.88154872103233</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.78084866634448</v>
       </c>
       <c r="E18">
-        <v>-29.9808774563394</v>
+        <v>-39.83480746194904</v>
       </c>
       <c r="F18">
-        <v>-1.705848027791099</v>
+        <v>-4.232601377569778</v>
       </c>
       <c r="G18">
-        <v>-9.832073111388315</v>
+        <v>-17.49202496706338</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.983785037778272</v>
       </c>
       <c r="E19">
-        <v>-30.55617253003683</v>
+        <v>-40.40990328279015</v>
       </c>
       <c r="F19">
-        <v>-1.53808623300874</v>
+        <v>-4.087848315767578</v>
       </c>
       <c r="G19">
-        <v>-9.870273496365964</v>
+        <v>-17.44876441322895</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.123196328586689</v>
       </c>
       <c r="E20">
-        <v>-30.89211511005886</v>
+        <v>-41.41988884072087</v>
       </c>
       <c r="F20">
-        <v>-1.374627806883925</v>
+        <v>-4.007524842187721</v>
       </c>
       <c r="G20">
-        <v>-9.691318646695121</v>
+        <v>-17.22910475087999</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.170123200729375</v>
       </c>
       <c r="E21">
-        <v>-32.74334622744648</v>
+        <v>-41.4358471831239</v>
       </c>
       <c r="F21">
-        <v>-1.235296409733048</v>
+        <v>-3.914678110212341</v>
       </c>
       <c r="G21">
-        <v>-9.718312835022338</v>
+        <v>-16.97994812777614</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>6.092038575280753</v>
       </c>
       <c r="E22">
-        <v>-32.3901886534843</v>
+        <v>-42.08171852423087</v>
       </c>
       <c r="F22">
-        <v>-1.106319605117165</v>
+        <v>-3.678059931807079</v>
       </c>
       <c r="G22">
-        <v>-9.551229601655322</v>
+        <v>-16.94265483227625</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.875414619955649</v>
       </c>
       <c r="E23">
-        <v>-32.88387836132652</v>
+        <v>-42.59339306659455</v>
       </c>
       <c r="F23">
-        <v>-0.9012547694519391</v>
+        <v>-3.709330801262761</v>
       </c>
       <c r="G23">
-        <v>-9.425875794810818</v>
+        <v>-16.78658743919116</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.514669998031007</v>
       </c>
       <c r="E24">
-        <v>-33.110870385198</v>
+        <v>-42.43809810744951</v>
       </c>
       <c r="F24">
-        <v>-0.9240381864985366</v>
+        <v>-3.441175019098116</v>
       </c>
       <c r="G24">
-        <v>-9.6049266503023</v>
+        <v>-16.78805732141059</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>8.0058563527163</v>
       </c>
       <c r="E25">
-        <v>-33.91333182901621</v>
+        <v>-42.41984156448759</v>
       </c>
       <c r="F25">
-        <v>-0.7891186741349699</v>
+        <v>-3.441860907307634</v>
       </c>
       <c r="G25">
-        <v>-9.232874300416848</v>
+        <v>-17.05654421991825</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>8.363041079063629</v>
       </c>
       <c r="E26">
-        <v>-34.27546030998759</v>
+        <v>-42.54913176164358</v>
       </c>
       <c r="F26">
-        <v>-0.8390095860707786</v>
+        <v>-3.545238674074804</v>
       </c>
       <c r="G26">
-        <v>-9.319266296809667</v>
+        <v>-16.94886376043515</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.600923475768175</v>
       </c>
       <c r="E27">
-        <v>-33.78667946796968</v>
+        <v>-42.7927930983373</v>
       </c>
       <c r="F27">
-        <v>-0.7024341672690158</v>
+        <v>-3.513547822345903</v>
       </c>
       <c r="G27">
-        <v>-9.280006537259451</v>
+        <v>-16.98274222821128</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.733758867729204</v>
       </c>
       <c r="E28">
-        <v>-34.02360017110298</v>
+        <v>-42.6911311211021</v>
       </c>
       <c r="F28">
-        <v>-0.5706955857321991</v>
+        <v>-3.422236883535314</v>
       </c>
       <c r="G28">
-        <v>-9.349279702668701</v>
+        <v>-17.46096046299562</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.783181063622177</v>
       </c>
       <c r="E29">
-        <v>-33.64766437288222</v>
+        <v>-42.76248855027796</v>
       </c>
       <c r="F29">
-        <v>-0.5565097939592576</v>
+        <v>-3.467371309844248</v>
       </c>
       <c r="G29">
-        <v>-9.449857386697298</v>
+        <v>-16.91020155435477</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.760567138016457</v>
       </c>
       <c r="E30">
-        <v>-33.65318684693457</v>
+        <v>-42.92242972375487</v>
       </c>
       <c r="F30">
-        <v>-0.5741159147383583</v>
+        <v>-3.267830856388291</v>
       </c>
       <c r="G30">
-        <v>-9.646536897185399</v>
+        <v>-16.92681387187083</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>8.677078140099011</v>
       </c>
       <c r="E31">
-        <v>-32.97333836534804</v>
+        <v>-42.5775977492558</v>
       </c>
       <c r="F31">
-        <v>-0.6278703322408238</v>
+        <v>-3.351611935507433</v>
       </c>
       <c r="G31">
-        <v>-9.235456525937479</v>
+        <v>-17.2401437649807</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.543071315142623</v>
       </c>
       <c r="E32">
-        <v>-32.71017062686629</v>
+        <v>-42.31445038890708</v>
       </c>
       <c r="F32">
-        <v>-0.7552483877693038</v>
+        <v>-3.452903044786952</v>
       </c>
       <c r="G32">
-        <v>-9.754205769759116</v>
+        <v>-17.28539395668422</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>8.356020888940353</v>
       </c>
       <c r="E33">
-        <v>-32.65933397765618</v>
+        <v>-42.05951994464527</v>
       </c>
       <c r="F33">
-        <v>-0.8191826122847724</v>
+        <v>-3.588497676583799</v>
       </c>
       <c r="G33">
-        <v>-9.431447442953411</v>
+        <v>-17.26459214378821</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>8.118707112704662</v>
       </c>
       <c r="E34">
-        <v>-32.16800586900897</v>
+        <v>-41.56372676062649</v>
       </c>
       <c r="F34">
-        <v>-0.6626592780561946</v>
+        <v>-3.352509885772068</v>
       </c>
       <c r="G34">
-        <v>-10.52293761779666</v>
+        <v>-17.36812945552892</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>7.828027586933241</v>
       </c>
       <c r="E35">
-        <v>-31.29622254508133</v>
+        <v>-41.54455320167802</v>
       </c>
       <c r="F35">
-        <v>-0.7441143015082756</v>
+        <v>-3.41124610483497</v>
       </c>
       <c r="G35">
-        <v>-10.04250793859209</v>
+        <v>-17.64442427569096</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>7.472244828572747</v>
       </c>
       <c r="E36">
-        <v>-31.64563507103917</v>
+        <v>-41.392222128771</v>
       </c>
       <c r="F36">
-        <v>-0.7035665455086426</v>
+        <v>-3.435494075449717</v>
       </c>
       <c r="G36">
-        <v>-10.01932749872611</v>
+        <v>-17.66407567401207</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>7.052256492921317</v>
       </c>
       <c r="E37">
-        <v>-30.95564054343846</v>
+        <v>-41.05968948967676</v>
       </c>
       <c r="F37">
-        <v>-0.732436806231011</v>
+        <v>-3.27906848857467</v>
       </c>
       <c r="G37">
-        <v>-9.770566485814195</v>
+        <v>-17.23227625350662</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.561427001127745</v>
       </c>
       <c r="E38">
-        <v>-30.47351429397483</v>
+        <v>-40.50641864931562</v>
       </c>
       <c r="F38">
-        <v>-0.6226027439264218</v>
+        <v>-3.472248737111931</v>
       </c>
       <c r="G38">
-        <v>-9.864480041672239</v>
+        <v>-17.74535618809225</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.992460485236002</v>
       </c>
       <c r="E39">
-        <v>-30.37117530987548</v>
+        <v>-40.00727665876817</v>
       </c>
       <c r="F39">
-        <v>-0.6412584062048694</v>
+        <v>-3.356822366471042</v>
       </c>
       <c r="G39">
-        <v>-10.18351069420073</v>
+        <v>-17.73326938632837</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.350654389716484</v>
       </c>
       <c r="E40">
-        <v>-30.23558600537482</v>
+        <v>-39.74691883840818</v>
       </c>
       <c r="F40">
-        <v>-0.7431094918486798</v>
+        <v>-3.405646341192045</v>
       </c>
       <c r="G40">
-        <v>-10.19530947850269</v>
+        <v>-17.47107583489086</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>4.632109167975003</v>
       </c>
       <c r="E41">
-        <v>-29.64757497666384</v>
+        <v>-38.96346792847416</v>
       </c>
       <c r="F41">
-        <v>-0.6012755967739457</v>
+        <v>-3.272095291777903</v>
       </c>
       <c r="G41">
-        <v>-10.06589694282704</v>
+        <v>-17.73130292227805</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.839602237015166</v>
       </c>
       <c r="E42">
-        <v>-28.7443187583829</v>
+        <v>-39.01988592189873</v>
       </c>
       <c r="F42">
-        <v>-0.6007429565339456</v>
+        <v>-3.263220163424309</v>
       </c>
       <c r="G42">
-        <v>-10.13686179700685</v>
+        <v>-17.75088810968838</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.981310886340208</v>
       </c>
       <c r="E43">
-        <v>-27.846988048341</v>
+        <v>-38.47578524140312</v>
       </c>
       <c r="F43">
-        <v>-0.4798493610345801</v>
+        <v>-3.250476559299642</v>
       </c>
       <c r="G43">
-        <v>-10.47017414299176</v>
+        <v>-17.71187001996253</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.059628308136704</v>
       </c>
       <c r="E44">
-        <v>-27.52401275363994</v>
+        <v>-37.9474323292692</v>
       </c>
       <c r="F44">
-        <v>-0.6683716996659</v>
+        <v>-3.208066633378515</v>
       </c>
       <c r="G44">
-        <v>-10.30426284274564</v>
+        <v>-17.55290093371226</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.089979190981293</v>
       </c>
       <c r="E45">
-        <v>-26.74859762083254</v>
+        <v>-37.38726915146839</v>
       </c>
       <c r="F45">
-        <v>-0.7104842416894214</v>
+        <v>-3.25852166351563</v>
       </c>
       <c r="G45">
-        <v>-10.16029714887936</v>
+        <v>-17.75168595116334</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.08534324276206859</v>
       </c>
       <c r="E46">
-        <v>-26.62954856764489</v>
+        <v>-37.3200892395646</v>
       </c>
       <c r="F46">
-        <v>-0.4360817409402655</v>
+        <v>-3.202447817285326</v>
       </c>
       <c r="G46">
-        <v>-10.63527435958075</v>
+        <v>-17.95934819647797</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.943859093004499</v>
       </c>
       <c r="E47">
-        <v>-26.16158964911426</v>
+        <v>-36.79950039611682</v>
       </c>
       <c r="F47">
-        <v>-0.6366874748762218</v>
+        <v>-3.189856632762774</v>
       </c>
       <c r="G47">
-        <v>-10.08503520658956</v>
+        <v>-17.93932601705646</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.975214090557478</v>
       </c>
       <c r="E48">
-        <v>-25.81035667660534</v>
+        <v>-36.3415244985361</v>
       </c>
       <c r="F48">
-        <v>-0.598394534947009</v>
+        <v>-3.168703442764886</v>
       </c>
       <c r="G48">
-        <v>-10.15362639961772</v>
+        <v>-17.87383846047137</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.994417363899271</v>
       </c>
       <c r="E49">
-        <v>-25.68404395110939</v>
+        <v>-36.23182674417429</v>
       </c>
       <c r="F49">
-        <v>-0.4972119417972578</v>
+        <v>-3.085303412651032</v>
       </c>
       <c r="G49">
-        <v>-10.20973352541729</v>
+        <v>-17.96119051507058</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.98661280494346</v>
       </c>
       <c r="E50">
-        <v>-24.7165807641107</v>
+        <v>-36.11462077990777</v>
       </c>
       <c r="F50">
-        <v>-0.4095151699650825</v>
+        <v>-3.075873278137562</v>
       </c>
       <c r="G50">
-        <v>-10.06528449190227</v>
+        <v>-17.84695186487418</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.927060444740419</v>
       </c>
       <c r="E51">
-        <v>-24.34761428738774</v>
+        <v>-35.19734440609908</v>
       </c>
       <c r="F51">
-        <v>-0.3151632944188161</v>
+        <v>-3.200814276767006</v>
       </c>
       <c r="G51">
-        <v>-10.39481950542687</v>
+        <v>-17.87156411568589</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.802258697119638</v>
       </c>
       <c r="E52">
-        <v>-23.63080666518761</v>
+        <v>-35.17605152131501</v>
       </c>
       <c r="F52">
-        <v>-0.7292683009153029</v>
+        <v>-3.180062016592073</v>
       </c>
       <c r="G52">
-        <v>-10.13794765594374</v>
+        <v>-18.27391623361952</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.596778503538666</v>
       </c>
       <c r="E53">
-        <v>-22.96676482212485</v>
+        <v>-34.93372155597955</v>
       </c>
       <c r="F53">
-        <v>-0.4859096969534614</v>
+        <v>-3.088746107577066</v>
       </c>
       <c r="G53">
-        <v>-10.66943256845495</v>
+        <v>-18.20325429435655</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.290986433090239</v>
       </c>
       <c r="E54">
-        <v>-22.81712139854138</v>
+        <v>-34.02091705025344</v>
       </c>
       <c r="F54">
-        <v>-0.5275807191512905</v>
+        <v>-3.099860313020427</v>
       </c>
       <c r="G54">
-        <v>-10.28768694123051</v>
+        <v>-17.9887458408667</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.878563568920316</v>
       </c>
       <c r="E55">
-        <v>-22.76032527753718</v>
+        <v>-34.18852493022533</v>
       </c>
       <c r="F55">
-        <v>-0.6325605484754746</v>
+        <v>-3.250094681926951</v>
       </c>
       <c r="G55">
-        <v>-10.59700114260124</v>
+        <v>-18.22199529265436</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.351069148097752</v>
       </c>
       <c r="E56">
-        <v>-22.08533811279788</v>
+        <v>-34.06513080622733</v>
       </c>
       <c r="F56">
-        <v>-0.4354041364047755</v>
+        <v>-3.060579959147077</v>
       </c>
       <c r="G56">
-        <v>-10.64018720916103</v>
+        <v>-18.18792481323695</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.704266726665015</v>
       </c>
       <c r="E57">
-        <v>-20.94270449423448</v>
+        <v>-33.61823155606937</v>
       </c>
       <c r="F57">
-        <v>-0.3545496793197241</v>
+        <v>-3.087485332390005</v>
       </c>
       <c r="G57">
-        <v>-10.67288877799795</v>
+        <v>-18.11972923040074</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.945490558764874</v>
       </c>
       <c r="E58">
-        <v>-21.16304192555169</v>
+        <v>-32.96541353583462</v>
       </c>
       <c r="F58">
-        <v>-0.5231398415048824</v>
+        <v>-3.199193161759727</v>
       </c>
       <c r="G58">
-        <v>-10.53783838326892</v>
+        <v>-18.40423585877293</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.07713388597287</v>
       </c>
       <c r="E59">
-        <v>-21.06132787086541</v>
+        <v>-33.1181340575063</v>
       </c>
       <c r="F59">
-        <v>-0.5266140143922234</v>
+        <v>-3.106751501444316</v>
       </c>
       <c r="G59">
-        <v>-10.71865375953283</v>
+        <v>-18.19357425919972</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.110349516772974</v>
       </c>
       <c r="E60">
-        <v>-20.83897979708879</v>
+        <v>-32.58545192422104</v>
       </c>
       <c r="F60">
-        <v>-0.5988998390627167</v>
+        <v>-3.193004428893412</v>
       </c>
       <c r="G60">
-        <v>-11.02890484529117</v>
+        <v>-18.54932217230426</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.0595412637949</v>
       </c>
       <c r="E61">
-        <v>-20.6825346055458</v>
+        <v>-32.77063707605371</v>
       </c>
       <c r="F61">
-        <v>-0.7261967145857223</v>
+        <v>-3.228793214163962</v>
       </c>
       <c r="G61">
-        <v>-10.90357421226545</v>
+        <v>-18.31450517720376</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.929811238199493</v>
       </c>
       <c r="E62">
-        <v>-19.84008900047687</v>
+        <v>-32.56477491190201</v>
       </c>
       <c r="F62">
-        <v>-0.7058213615790629</v>
+        <v>-3.246387737799423</v>
       </c>
       <c r="G62">
-        <v>-10.82266447928566</v>
+        <v>-18.53604357414624</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.737564731743008</v>
       </c>
       <c r="E63">
-        <v>-19.98773989549696</v>
+        <v>-32.42410692380175</v>
       </c>
       <c r="F63">
-        <v>-0.6743102655765697</v>
+        <v>-3.329369442374864</v>
       </c>
       <c r="G63">
-        <v>-11.04058113940818</v>
+        <v>-18.32044926171952</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.49363892623292</v>
       </c>
       <c r="E64">
-        <v>-20.06737311092184</v>
+        <v>-32.24702547620581</v>
       </c>
       <c r="F64">
-        <v>-0.852142522874762</v>
+        <v>-3.196427243001779</v>
       </c>
       <c r="G64">
-        <v>-10.78100126367393</v>
+        <v>-18.55650936667002</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.200035031649866</v>
       </c>
       <c r="E65">
-        <v>-19.77617864680661</v>
+        <v>-32.12974252788116</v>
       </c>
       <c r="F65">
-        <v>-0.9809519972752795</v>
+        <v>-3.345153983235209</v>
       </c>
       <c r="G65">
-        <v>-10.83341713119721</v>
+        <v>-18.73890718370171</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.871195375281608</v>
       </c>
       <c r="E66">
-        <v>-19.23751666359422</v>
+        <v>-32.09355096361185</v>
       </c>
       <c r="F66">
-        <v>-0.8580396704152916</v>
+        <v>-3.427733101252888</v>
       </c>
       <c r="G66">
-        <v>-10.91759106207872</v>
+        <v>-18.65431612408225</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.51024229504558</v>
       </c>
       <c r="E67">
-        <v>-19.6434536021158</v>
+        <v>-31.99322035773491</v>
       </c>
       <c r="F67">
-        <v>-1.197913017212109</v>
+        <v>-3.616580159906106</v>
       </c>
       <c r="G67">
-        <v>-11.17539648540392</v>
+        <v>-18.60966348584856</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.115432402266973</v>
       </c>
       <c r="E68">
-        <v>-19.88820403680836</v>
+        <v>-31.84094815499</v>
       </c>
       <c r="F68">
-        <v>-0.9721497652531319</v>
+        <v>-3.623405907305174</v>
       </c>
       <c r="G68">
-        <v>-10.86549300692721</v>
+        <v>-18.228055246264</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.69608581050768</v>
       </c>
       <c r="E69">
-        <v>-18.85509156212047</v>
+        <v>-32.01299393948941</v>
       </c>
       <c r="F69">
-        <v>-1.169950647163209</v>
+        <v>-3.578553125913192</v>
       </c>
       <c r="G69">
-        <v>-10.66843609424763</v>
+        <v>-18.3998874572071</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.250422971306216</v>
       </c>
       <c r="E70">
-        <v>-18.91663352388471</v>
+        <v>-31.85879260681722</v>
       </c>
       <c r="F70">
-        <v>-1.248859269219084</v>
+        <v>-3.708065884238686</v>
       </c>
       <c r="G70">
-        <v>-10.74291343724461</v>
+        <v>-18.30700844683007</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.778375812811863</v>
       </c>
       <c r="E71">
-        <v>-18.70953735056593</v>
+        <v>-31.83588532104942</v>
       </c>
       <c r="F71">
-        <v>-1.317989842452314</v>
+        <v>-3.746400242538038</v>
       </c>
       <c r="G71">
-        <v>-10.76219074391979</v>
+        <v>-18.18809034051392</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.287417995152115</v>
       </c>
       <c r="E72">
-        <v>-19.528443947743</v>
+        <v>-31.91073193944819</v>
       </c>
       <c r="F72">
-        <v>-1.647111808728197</v>
+        <v>-3.772064721411573</v>
       </c>
       <c r="G72">
-        <v>-10.41381210518566</v>
+        <v>-18.19980967172294</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.775755391535998</v>
       </c>
       <c r="E73">
-        <v>-19.05766378990559</v>
+        <v>-31.41274018129869</v>
       </c>
       <c r="F73">
-        <v>-1.442160459397155</v>
+        <v>-3.980397466480843</v>
       </c>
       <c r="G73">
-        <v>-10.50873868797873</v>
+        <v>-18.32420176508828</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.247254651541983</v>
       </c>
       <c r="E74">
-        <v>-19.47418377218309</v>
+        <v>-31.91620007181246</v>
       </c>
       <c r="F74">
-        <v>-1.537672877674743</v>
+        <v>-3.939448780658255</v>
       </c>
       <c r="G74">
-        <v>-9.950948180612464</v>
+        <v>-17.88922091031959</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.709105712538411</v>
       </c>
       <c r="E75">
-        <v>-19.43373544234658</v>
+        <v>-32.27661905384593</v>
       </c>
       <c r="F75">
-        <v>-1.694492767433523</v>
+        <v>-3.893314514894142</v>
       </c>
       <c r="G75">
-        <v>-10.20789286209746</v>
+        <v>-18.02925367608522</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.162230302140536</v>
       </c>
       <c r="E76">
-        <v>-19.97670853281427</v>
+        <v>-31.76925335450056</v>
       </c>
       <c r="F76">
-        <v>-1.890094333889168</v>
+        <v>-4.155179675001928</v>
       </c>
       <c r="G76">
-        <v>-9.988612257212752</v>
+        <v>-17.99512360684811</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.616487135106589</v>
       </c>
       <c r="E77">
-        <v>-20.42012765069734</v>
+        <v>-32.18500349619676</v>
       </c>
       <c r="F77">
-        <v>-2.048901477047264</v>
+        <v>-4.244242424681319</v>
       </c>
       <c r="G77">
-        <v>-9.917544776121218</v>
+        <v>-17.75928365317597</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.081488477034223</v>
       </c>
       <c r="E78">
-        <v>-20.55682416709287</v>
+        <v>-32.82255150207764</v>
       </c>
       <c r="F78">
-        <v>-2.088894226887021</v>
+        <v>-4.182643367874342</v>
       </c>
       <c r="G78">
-        <v>-9.646963957559965</v>
+        <v>-17.6293215669408</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.562260237519471</v>
       </c>
       <c r="E79">
-        <v>-20.16281975758151</v>
+        <v>-32.48449638893104</v>
       </c>
       <c r="F79">
-        <v>-2.050266626527077</v>
+        <v>-4.445960656039235</v>
       </c>
       <c r="G79">
-        <v>-10.05188009301376</v>
+        <v>-17.51255531522516</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.071540810934668</v>
       </c>
       <c r="E80">
-        <v>-21.02272715842403</v>
+        <v>-32.77530819699262</v>
       </c>
       <c r="F80">
-        <v>-2.166073217805851</v>
+        <v>-4.327799844601706</v>
       </c>
       <c r="G80">
-        <v>-9.403479954237648</v>
+        <v>-17.52200030164871</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.6184730908661167</v>
       </c>
       <c r="E81">
-        <v>-21.53408244337016</v>
+        <v>-33.443258113124</v>
       </c>
       <c r="F81">
-        <v>-2.037778159562472</v>
+        <v>-4.436957959105611</v>
       </c>
       <c r="G81">
-        <v>-9.159472884720126</v>
+        <v>-17.12970065524507</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.2080003936624747</v>
       </c>
       <c r="E82">
-        <v>-22.11364107534582</v>
+        <v>-33.59815456655636</v>
       </c>
       <c r="F82">
-        <v>-1.844064442417808</v>
+        <v>-4.297488224598466</v>
       </c>
       <c r="G82">
-        <v>-9.076778767694671</v>
+        <v>-17.65710366510636</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.1483677448302302</v>
       </c>
       <c r="E83">
-        <v>-22.51022671504156</v>
+        <v>-33.87525868379672</v>
       </c>
       <c r="F83">
-        <v>-2.124531420922859</v>
+        <v>-4.501326248140145</v>
       </c>
       <c r="G83">
-        <v>-8.664086160769125</v>
+        <v>-17.40942189004025</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.4438902299234786</v>
       </c>
       <c r="E84">
-        <v>-23.48860352439874</v>
+        <v>-34.67430112973914</v>
       </c>
       <c r="F84">
-        <v>-2.3809094753545</v>
+        <v>-4.410644868555684</v>
       </c>
       <c r="G84">
-        <v>-8.76840145071156</v>
+        <v>-17.33617441471111</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.6756486420001843</v>
       </c>
       <c r="E85">
-        <v>-23.96498993305765</v>
+        <v>-35.34908904162211</v>
       </c>
       <c r="F85">
-        <v>-2.199899600699169</v>
+        <v>-4.472747572743563</v>
       </c>
       <c r="G85">
-        <v>-8.592032137106887</v>
+        <v>-16.96650896815947</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.8366802555638656</v>
       </c>
       <c r="E86">
-        <v>-24.8010639751978</v>
+        <v>-35.75118583418518</v>
       </c>
       <c r="F86">
-        <v>-2.356859484549022</v>
+        <v>-4.668359907975444</v>
       </c>
       <c r="G86">
-        <v>-8.534249875264448</v>
+        <v>-17.28245419224535</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9240155300006638</v>
       </c>
       <c r="E87">
-        <v>-26.263570883767</v>
+        <v>-36.32076144521093</v>
       </c>
       <c r="F87">
-        <v>-2.364204618309645</v>
+        <v>-4.658644815075411</v>
       </c>
       <c r="G87">
-        <v>-8.561750577059174</v>
+        <v>-17.31685572621669</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9387905056570568</v>
       </c>
       <c r="E88">
-        <v>-26.94074077297799</v>
+        <v>-36.89804225476073</v>
       </c>
       <c r="F88">
-        <v>-2.266898784604995</v>
+        <v>-4.572564188046098</v>
       </c>
       <c r="G88">
-        <v>-8.35431841465952</v>
+        <v>-16.87655813531193</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>0.8782715014566809</v>
       </c>
       <c r="E89">
-        <v>-28.3527099116216</v>
+        <v>-37.83689680721597</v>
       </c>
       <c r="F89">
-        <v>-2.325316910585222</v>
+        <v>-4.730187594185593</v>
       </c>
       <c r="G89">
-        <v>-8.062391198461048</v>
+        <v>-16.95893112942007</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>0.7431188692381173</v>
       </c>
       <c r="E90">
-        <v>-29.597480997191</v>
+        <v>-38.86599931817007</v>
       </c>
       <c r="F90">
-        <v>-2.307695050825469</v>
+        <v>-4.893891217061637</v>
       </c>
       <c r="G90">
-        <v>-8.458719778785976</v>
+        <v>-17.14374067887712</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>0.5388688366810038</v>
       </c>
       <c r="E91">
-        <v>-30.76849909083447</v>
+        <v>-39.69666862658206</v>
       </c>
       <c r="F91">
-        <v>-2.617772850510991</v>
+        <v>-4.772442615402396</v>
       </c>
       <c r="G91">
-        <v>-8.642653688947883</v>
+        <v>-16.80281407815189</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.2677509059692713</v>
       </c>
       <c r="E92">
-        <v>-32.23555938001839</v>
+        <v>-40.73365294654651</v>
       </c>
       <c r="F92">
-        <v>-2.754094788887497</v>
+        <v>-4.978098077025818</v>
       </c>
       <c r="G92">
-        <v>-8.362055159584797</v>
+        <v>-17.12104357865988</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.06534405445717777</v>
       </c>
       <c r="E93">
-        <v>-33.21697705967172</v>
+        <v>-41.68839565005766</v>
       </c>
       <c r="F93">
-        <v>-2.869288388288199</v>
+        <v>-5.116295439202262</v>
       </c>
       <c r="G93">
-        <v>-8.592091726926595</v>
+        <v>-17.50626527870055</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.4496965766729294</v>
       </c>
       <c r="E94">
-        <v>-34.9637430744134</v>
+        <v>-42.49656976383655</v>
       </c>
       <c r="F94">
-        <v>-2.866216801958618</v>
+        <v>-5.103335631185464</v>
       </c>
       <c r="G94">
-        <v>-8.78698023227795</v>
+        <v>-17.32226350235509</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.878287716994402</v>
       </c>
       <c r="E95">
-        <v>-36.76099025315559</v>
+        <v>-43.77407945224441</v>
       </c>
       <c r="F95">
-        <v>-3.03583165462104</v>
+        <v>-5.167883675946407</v>
       </c>
       <c r="G95">
-        <v>-9.148594432078081</v>
+        <v>-17.14906072555873</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.345850723058166</v>
       </c>
       <c r="E96">
-        <v>-38.44821362740742</v>
+        <v>-45.54198891212791</v>
       </c>
       <c r="F96">
-        <v>-3.068436195595228</v>
+        <v>-5.340952820678502</v>
       </c>
       <c r="G96">
-        <v>-9.047480439672121</v>
+        <v>-17.40989529805237</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.833006559121428</v>
       </c>
       <c r="E97">
-        <v>-40.40333020276801</v>
+        <v>-46.75680867061057</v>
       </c>
       <c r="F97">
-        <v>-3.049868340261477</v>
+        <v>-5.554227605672874</v>
       </c>
       <c r="G97">
-        <v>-9.834701684546495</v>
+        <v>-18.15215767923067</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.341810808947363</v>
       </c>
       <c r="E98">
-        <v>-42.10631266656653</v>
+        <v>-47.86109969975103</v>
       </c>
       <c r="F98">
-        <v>-3.230408530599421</v>
+        <v>-5.378414908102707</v>
       </c>
       <c r="G98">
-        <v>-9.708977096601593</v>
+        <v>-17.90830620535349</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.84681426479682</v>
       </c>
       <c r="E99">
-        <v>-44.05894990240792</v>
+        <v>-49.4531175685841</v>
       </c>
       <c r="F99">
-        <v>-3.280303584372243</v>
+        <v>-5.619152557602091</v>
       </c>
       <c r="G99">
-        <v>-9.888746340475098</v>
+        <v>-18.18322549384396</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.361782372438512</v>
       </c>
       <c r="E100">
-        <v>-45.58963751563661</v>
+        <v>-50.77730337070751</v>
       </c>
       <c r="F100">
-        <v>-3.499568294056259</v>
+        <v>-5.810046512107625</v>
       </c>
       <c r="G100">
-        <v>-10.28950443073157</v>
+        <v>-18.63876980222983</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.842894746229172</v>
       </c>
       <c r="E101">
-        <v>-47.98041819714213</v>
+        <v>-52.18256697146425</v>
       </c>
       <c r="F101">
-        <v>-3.61422014117553</v>
+        <v>-5.82256728540094</v>
       </c>
       <c r="G101">
-        <v>-10.45136362323762</v>
+        <v>-18.67507655515902</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.352879825495098</v>
       </c>
       <c r="E102">
-        <v>-49.83255274509428</v>
+        <v>-54.0815723575143</v>
       </c>
       <c r="F102">
-        <v>-3.618294880429901</v>
+        <v>-5.787004644431355</v>
       </c>
       <c r="G102">
-        <v>-10.76350834104442</v>
+        <v>-18.52889610632696</v>
       </c>
     </row>
   </sheetData>
